--- a/firm.xlsx
+++ b/firm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\buscadorANC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08782088-1094-4E5C-B160-FEF1029442E9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BEDF2E-64A0-4706-8DCE-7C0493E13C60}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6021" uniqueCount="4289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6024" uniqueCount="4291">
   <si>
     <t>tipo</t>
   </si>
@@ -12990,6 +12990,12 @@
   </si>
   <si>
     <t>“EXXONMOBIL INTERNATIONAL HOLDING INC. Y BRIDAS CORPORATION S/ NOTIFICACION ARTICULO 8º LEY Nº 25.156 (CONC. 887).</t>
+  </si>
+  <si>
+    <t>proyectos de energía renovable y generación de electricidad por medio de fuentes de energía renovables.</t>
+  </si>
+  <si>
+    <t>[{"rol": "objeto", "nombre": "TOTAL EREN S.A."}, {"rol": "objeto", "nombre": "VIENTOS LOS HÉRCULES S.A."}]</t>
   </si>
 </sst>
 </file>
@@ -31081,17 +31087,26 @@
       <c r="F459" t="s">
         <v>1665</v>
       </c>
+      <c r="G459" t="s">
+        <v>4290</v>
+      </c>
       <c r="H459" s="3">
         <v>44924</v>
       </c>
       <c r="I459" s="3">
         <v>45148</v>
       </c>
+      <c r="J459" t="s">
+        <v>18</v>
+      </c>
       <c r="K459" t="s">
         <v>1663</v>
       </c>
       <c r="L459" t="s">
         <v>1664</v>
+      </c>
+      <c r="P459" t="s">
+        <v>4289</v>
       </c>
       <c r="S459">
         <v>2023</v>
